--- a/PnL_Momentum_Maxfolio.xlsx
+++ b/PnL_Momentum_Maxfolio.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,16 +489,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.659771612172982</v>
+        <v>3.729576874738165</v>
       </c>
       <c r="D2" t="n">
-        <v>3.676215404870192</v>
+        <v>3.74633431085044</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004493119910137233</v>
+        <v>0.004493119910137677</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01644379269720986</v>
+        <v>0.01675743611227531</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>45992</v>
@@ -515,29 +515,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIIL</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.75</v>
+        <v>3.754172396617011</v>
       </c>
       <c r="D3" t="n">
-        <v>3.704489460717219</v>
+        <v>3.500044923325059</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01213614380874151</v>
+        <v>-0.06769200943487652</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.04551053928278082</v>
+        <v>-0.2541274732919518</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>45972</v>
+        <v>46023</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45989</v>
+        <v>46052</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -548,29 +548,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.75</v>
+        <v>3.286094172548674</v>
       </c>
       <c r="D4" t="n">
-        <v>3.511742682096665</v>
+        <v>2.915977909492861</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06353528477422266</v>
+        <v>-0.1126310579129731</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2382573179033352</v>
+        <v>-0.370116263055813</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>45972</v>
+        <v>46083</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45989</v>
+        <v>46093</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -581,29 +581,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3.692863669683879</v>
+        <v>3.329454071556786</v>
       </c>
       <c r="D5" t="n">
-        <v>3.582372482306992</v>
+        <v>3.140844883434637</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0299201912824324</v>
+        <v>-0.05664868295779169</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.110491187376887</v>
+        <v>-0.188609188122149</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46045</v>
+        <v>46093</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -621,16 +621,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.661514542307075</v>
+        <v>3.731353048940068</v>
       </c>
       <c r="D6" t="n">
-        <v>3.831011270199248</v>
+        <v>3.904082700863648</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0462914255654916</v>
+        <v>0.04629142556549182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1694967278921728</v>
+        <v>0.1727296519235799</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>45992</v>
@@ -647,29 +647,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.75</v>
+        <v>3.387994716095842</v>
       </c>
       <c r="D7" t="n">
-        <v>4.035103286718252</v>
+        <v>3.497945305584181</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07602754312486715</v>
+        <v>0.03245299910474486</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2851032867182521</v>
+        <v>0.109950589488339</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>45972</v>
+        <v>46054</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45989</v>
+        <v>46080</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -680,29 +680,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.697682545576364</v>
+        <v>3.235004527370492</v>
       </c>
       <c r="D8" t="n">
-        <v>3.717340868238272</v>
+        <v>2.95840753494462</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005316390041493868</v>
+        <v>-0.08550126903553312</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01965832266190803</v>
+        <v>-0.2765969924258722</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46023</v>
+        <v>46083</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46045</v>
+        <v>46093</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -713,29 +713,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.75</v>
+        <v>3.17548743643422</v>
       </c>
       <c r="D9" t="n">
-        <v>3.438646866929455</v>
+        <v>3.230368234989983</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.08302750215214527</v>
+        <v>0.01728263759638393</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3113531330705448</v>
+        <v>0.05488079855576311</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>45972</v>
+        <v>46054</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46045</v>
+        <v>46093</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -746,29 +746,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.75</v>
+        <v>3.249130017225665</v>
       </c>
       <c r="D10" t="n">
-        <v>3.715996279934899</v>
+        <v>3.057567410984722</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.009067658684026925</v>
+        <v>-0.05895812270526268</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.03400372006510111</v>
+        <v>-0.191562606240943</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>45972</v>
+        <v>46083</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45989</v>
+        <v>46093</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -779,29 +779,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>3.717374900186652</v>
+        <v>3.759071275231678</v>
       </c>
       <c r="D11" t="n">
-        <v>3.660509576473179</v>
+        <v>3.409826647547095</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01529717212827186</v>
+        <v>-0.09290715767634883</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05686532371347264</v>
+        <v>-0.3492446276845831</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46045</v>
+        <v>46093</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -812,29 +812,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3.75</v>
+        <v>3.804333266358582</v>
       </c>
       <c r="D12" t="n">
-        <v>3.492375113993313</v>
+        <v>3.442920768870137</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06869996960178315</v>
+        <v>-0.09500022006073638</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.257624886006687</v>
+        <v>-0.3614124974884452</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>45972</v>
+        <v>45992</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45989</v>
+        <v>46052</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -845,29 +845,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3.75</v>
+        <v>3.788278868646771</v>
       </c>
       <c r="D13" t="n">
-        <v>3.564444684528954</v>
+        <v>3.786683915786489</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.04948141745894563</v>
+        <v>-0.0004210230860992592</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1855553154710461</v>
+        <v>-0.001594952860282106</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>45972</v>
+        <v>45992</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45989</v>
+        <v>46052</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOLDBEES</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>3.431923038373986</v>
       </c>
       <c r="D14" t="n">
-        <v>25.32190918772387</v>
+        <v>3.26700776083725</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01287636750895471</v>
+        <v>-0.04805331462644669</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3219091877238682</v>
+        <v>-0.164915277536736</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>45972</v>
+        <v>46054</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45989</v>
+        <v>46093</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>EQUITIES</t>
         </is>
       </c>
     </row>
@@ -915,25 +915,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>15.49811211292372</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>18.5448736583617</v>
+        <v>13.15136697408715</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1965892053973022</v>
+        <v>-0.1232422017275233</v>
       </c>
       <c r="F15" t="n">
-        <v>3.046761545437979</v>
+        <v>-1.84863302591285</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46045</v>
+        <v>46093</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -951,22 +951,22 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>3.721142453636607</v>
+        <v>3.78292066344223</v>
       </c>
       <c r="D16" t="n">
-        <v>3.483162412997057</v>
+        <v>3.526090715924211</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0639534883720928</v>
+        <v>-0.06789197299324778</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2379800406395498</v>
+        <v>-0.2568299475180189</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -984,22 +984,22 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>3.75</v>
+        <v>3.685009032403749</v>
       </c>
       <c r="D17" t="n">
-        <v>2.705378696439348</v>
+        <v>2.899189906288812</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2785656809495072</v>
+        <v>-0.2132475440914574</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.044621303560652</v>
+        <v>-0.7858191261149372</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>45972</v>
+        <v>45992</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46045</v>
+        <v>46080</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1017,22 +1017,22 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>3.75</v>
+        <v>3.823487731800146</v>
       </c>
       <c r="D18" t="n">
-        <v>3.767305029995383</v>
+        <v>3.361000890760385</v>
       </c>
       <c r="E18" t="n">
-        <v>0.004614674665435414</v>
+        <v>-0.1209594154554842</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01730502999538297</v>
+        <v>-0.4624868410397607</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>45972</v>
+        <v>45992</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1050,22 +1050,22 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>3.75</v>
+        <v>3.761133102424543</v>
       </c>
       <c r="D19" t="n">
-        <v>4.52385826771653</v>
+        <v>4.363016452251357</v>
       </c>
       <c r="E19" t="n">
-        <v>0.206362204724408</v>
+        <v>0.1600271336951147</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7738582677165304</v>
+        <v>0.6018833498268141</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>45972</v>
+        <v>45992</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46045</v>
+        <v>46093</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1083,22 +1083,22 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>3.75</v>
+        <v>3.026236708377632</v>
       </c>
       <c r="D20" t="n">
-        <v>3.409090909090909</v>
+        <v>2.661118787617176</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.09090909090909094</v>
+        <v>-0.1206508135168963</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3409090909090908</v>
+        <v>-0.365117920760456</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>45972</v>
+        <v>46054</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45989</v>
+        <v>46093</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1109,29 +1109,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>3.75</v>
+        <v>3.141965515216141</v>
       </c>
       <c r="D21" t="n">
-        <v>3.702249575551783</v>
+        <v>3.327694751951424</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01273344651952457</v>
+        <v>0.05911243641466446</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0477504244482172</v>
+        <v>0.1857292367352827</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>45972</v>
+        <v>46054</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45989</v>
+        <v>46080</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1149,22 +1149,22 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>3.75</v>
+        <v>3.836932140511178</v>
       </c>
       <c r="D22" t="n">
-        <v>4.013176144244105</v>
+        <v>3.269539886676219</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07018030513176132</v>
+        <v>-0.147876541220082</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2631761442441052</v>
+        <v>-0.5673922538349587</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>45972</v>
+        <v>46023</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45989</v>
+        <v>46052</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1175,29 +1175,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>3.774271878804619</v>
+        <v>3.823685722493536</v>
       </c>
       <c r="D23" t="n">
-        <v>3.396814275323556</v>
+        <v>3.60779948290721</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1000080586670961</v>
+        <v>-0.05646024680227646</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3774576034810631</v>
+        <v>-0.2158862395863257</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46045</v>
+        <v>46022</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>3.75</v>
+        <v>3.203380626262871</v>
       </c>
       <c r="D24" t="n">
-        <v>3.617568268233669</v>
+        <v>3.472561101113994</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.03531512847102158</v>
+        <v>0.08403012512601538</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1324317317663311</v>
+        <v>0.2691804748511228</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>45972</v>
+        <v>46054</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1241,29 +1241,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>3.75</v>
+        <v>3.156931568033881</v>
       </c>
       <c r="D25" t="n">
-        <v>3.796410046410046</v>
+        <v>2.820281504109771</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01237601237601216</v>
+        <v>-0.106638378649992</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04641004641004587</v>
+        <v>-0.3366500639241101</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>45972</v>
+        <v>46083</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45989</v>
+        <v>46093</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1281,22 +1281,22 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>3.816801806807284</v>
+        <v>3.880168148124581</v>
       </c>
       <c r="D26" t="n">
-        <v>3.807567311000625</v>
+        <v>3.763383836301609</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.002419432884932404</v>
+        <v>-0.03009774508855179</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.009234495806659027</v>
+        <v>-0.1167843118229719</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46045</v>
+        <v>46080</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1314,22 +1314,22 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>3.777908432159983</v>
+        <v>3.84062906773262</v>
       </c>
       <c r="D27" t="n">
-        <v>3.304646579369927</v>
+        <v>3.700274599898645</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1252708638360176</v>
+        <v>-0.03654465592972134</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4732618527900558</v>
+        <v>-0.140354467833975</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1347,22 +1347,22 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>3.75</v>
+        <v>3.742909778445727</v>
       </c>
       <c r="D28" t="n">
-        <v>3.903317439383179</v>
+        <v>3.508750666602026</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04088465050218115</v>
+        <v>-0.06256071497960003</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1533174393831791</v>
+        <v>-0.234159111843701</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>45972</v>
+        <v>45992</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1373,29 +1373,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>3.75</v>
+        <v>18.99949059054711</v>
       </c>
       <c r="D29" t="n">
-        <v>3.707422470767668</v>
+        <v>19.02135421608283</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0113540077952885</v>
+        <v>0.001150747986190526</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.04257752923233182</v>
+        <v>0.02186362553571897</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>45972</v>
+        <v>46083</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46045</v>
+        <v>46093</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1406,29 +1406,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3.713613763803158</v>
+        <v>3.711581559148391</v>
       </c>
       <c r="D30" t="n">
-        <v>3.659893873518155</v>
+        <v>3.437850168080679</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0144656643640797</v>
+        <v>-0.07375060650169807</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.05371989028500312</v>
+        <v>-0.2737313910677122</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1439,29 +1439,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>3.640723445087814</v>
+        <v>3.784445993602887</v>
       </c>
       <c r="D31" t="n">
-        <v>3.561555770282969</v>
+        <v>3.729701468055442</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.02174503941288386</v>
+        <v>-0.01446566436407959</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.07916767480484488</v>
+        <v>-0.05474452554744502</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46045</v>
+        <v>46022</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1472,29 +1472,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>M&amp;MFIN</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>3.725405129771196</v>
+        <v>3.710165389269866</v>
       </c>
       <c r="D32" t="n">
-        <v>3.86426597824375</v>
+        <v>3.486789027833802</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0372740262160649</v>
+        <v>-0.06020657787442274</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1388608484725542</v>
+        <v>-0.2233763614360642</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1505,29 +1505,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>3.729675432270496</v>
+        <v>3.181410155140579</v>
       </c>
       <c r="D33" t="n">
-        <v>4.067939825050364</v>
+        <v>2.946715963367914</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09069539666993065</v>
+        <v>-0.07377049180327844</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3382643927798679</v>
+        <v>-0.234694191772665</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>45992</v>
+        <v>46083</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1538,56 +1538,56 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MOGSEC</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>5.053120506085769</v>
+        <v>3.796462264150943</v>
       </c>
       <c r="D34" t="n">
-        <v>5.058751172042885</v>
+        <v>3.937971698113207</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001114294810570016</v>
+        <v>0.03727402621606513</v>
       </c>
       <c r="F34" t="n">
-        <v>0.005630665957116143</v>
+        <v>0.141509433962264</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46045</v>
+        <v>46022</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DEBT</t>
+          <t>EQUITIES</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>3.745562031879837</v>
+        <v>3.800814016975232</v>
       </c>
       <c r="D35" t="n">
-        <v>3.746151713918917</v>
+        <v>4.145530351913434</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0001574348613269105</v>
+        <v>0.09069539666993109</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0005896820390800528</v>
+        <v>0.3447163349382025</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>45992</v>
@@ -1604,29 +1604,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>3.733881580956574</v>
+        <v>3.060029768855503</v>
       </c>
       <c r="D36" t="n">
-        <v>5.363031580835649</v>
+        <v>3.409426442413982</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4363153904473069</v>
+        <v>0.1141808086687859</v>
       </c>
       <c r="F36" t="n">
-        <v>1.629149999879075</v>
+        <v>0.3493966735584793</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>45992</v>
+        <v>46054</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46045</v>
+        <v>46093</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1637,62 +1637,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>MOGSEC</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>3.532859146463635</v>
+        <v>18.99949059054711</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.05790422760969727</v>
+        <v>2.799898118109422</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2171408535363648</v>
+        <v>13.99949059054711</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>45972</v>
+        <v>45992</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45989</v>
+        <v>46080</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EQUITIES</t>
+          <t>DEBT</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>3.646636216939378</v>
+        <v>3.8170036322846</v>
       </c>
       <c r="D38" t="n">
-        <v>3.272886978396892</v>
+        <v>3.817604561722133</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.102491506228766</v>
+        <v>0.0001574348613269105</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3737492385424859</v>
+        <v>0.0006009294375330931</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46045</v>
+        <v>46022</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1703,29 +1703,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>3.75</v>
+        <v>3.159462895412427</v>
       </c>
       <c r="D39" t="n">
-        <v>3.655166591625394</v>
+        <v>3.03319653596106</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.02528890889989499</v>
+        <v>-0.03996450144570673</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.09483340837460608</v>
+        <v>-0.1262663594513667</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>45972</v>
+        <v>46054</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1736,29 +1736,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>3.75</v>
+        <v>3.805100392337872</v>
       </c>
       <c r="D40" t="n">
-        <v>3.730171682224688</v>
+        <v>5.684571890145388</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.005287551406749857</v>
+        <v>0.4939347990902179</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.0198283177753118</v>
+        <v>1.879471497807516</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>45972</v>
+        <v>45992</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1769,29 +1769,29 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>3.663641254568063</v>
+        <v>3.716190939358797</v>
       </c>
       <c r="D41" t="n">
-        <v>3.362006449534477</v>
+        <v>3.331805768583291</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.08233197086573063</v>
+        <v>-0.1034352585881471</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.3016348050335864</v>
+        <v>-0.3843851707755062</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1802,29 +1802,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>3.723386504675748</v>
+        <v>3.884029986369832</v>
       </c>
       <c r="D42" t="n">
-        <v>3.953274191382309</v>
+        <v>3.68838028169014</v>
       </c>
       <c r="E42" t="n">
-        <v>0.06174155877126197</v>
+        <v>-0.05037286152946363</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2298876867065611</v>
+        <v>-0.1956497046796919</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>46045</v>
+        <v>46022</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1835,29 +1835,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>3.801350739637638</v>
+        <v>3.715361445783132</v>
       </c>
       <c r="D43" t="n">
-        <v>3.761834884150574</v>
+        <v>3.824799196787149</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.01039521427870949</v>
+        <v>0.02945547898932599</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.03951585548706404</v>
+        <v>0.109437751004017</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46045</v>
+        <v>46022</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -1868,62 +1868,62 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SILVERBEES</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>5.369336641538433</v>
+        <v>3.724464832514145</v>
       </c>
       <c r="D44" t="n">
-        <v>9.64451870724565</v>
+        <v>3.237087492803483</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7962216473136399</v>
+        <v>-0.1308583545898767</v>
       </c>
       <c r="F44" t="n">
-        <v>4.275182065707217</v>
+        <v>-0.4873773397106618</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>EQUITIES</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>3.647511783652773</v>
+        <v>3.40652398078372</v>
       </c>
       <c r="D45" t="n">
-        <v>3.289063728165586</v>
+        <v>3.46657304779343</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.09827193899514197</v>
+        <v>0.01762766601628174</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.3584480554871869</v>
+        <v>0.06004906700971002</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>45992</v>
+        <v>46054</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -1934,31 +1934,196 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>3.702991932448794</v>
+        <v>3.785201970097795</v>
       </c>
       <c r="D46" t="n">
-        <v>4.27351014522216</v>
+        <v>4.141716296298934</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1540695262590221</v>
+        <v>0.09418634171109441</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5705182127733663</v>
+        <v>0.3565143262011388</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46045</v>
+        <v>46093</v>
       </c>
       <c r="I46" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3.864460563156646</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3.883409570527229</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.004903402961655479</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.01894900737058292</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SILVERBEES</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8.618013356597075</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.723602671319415</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.618013356597075</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3.71708320633953</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3.351798232246265</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.09827193899514197</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.3652849740932651</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.245561253581092</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3.428755240616786</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.05644447068548186</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1831939870356938</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.764468808263581</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4.415981455242576</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.173068945490749</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.6515126469789947</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>EQUITIES</t>
         </is>

--- a/PnL_Momentum_Maxfolio.xlsx
+++ b/PnL_Momentum_Maxfolio.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,51 +417,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>trade_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>buy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>sell</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Profit/Loss%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Profit/Loss</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Buy Date</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Sell Date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Asset_Class</t>
         </is>
@@ -500,10 +488,10 @@
       <c r="F2" t="n">
         <v>0.01675743611227531</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="I2" t="inlineStr">
@@ -522,21 +510,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.754172396617011</v>
+        <v>3.755363536148944</v>
       </c>
       <c r="D3" t="n">
-        <v>3.500044923325059</v>
+        <v>3.501155432228559</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06769200943487652</v>
+        <v>-0.06769200943487641</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2541274732919518</v>
-      </c>
-      <c r="G3" s="2" t="n">
+        <v>-0.254208103920385</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="I3" t="inlineStr">
@@ -555,22 +543,22 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.286094172548674</v>
+        <v>3.286613068136427</v>
       </c>
       <c r="D4" t="n">
-        <v>2.915977909492861</v>
+        <v>2.864676017180514</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1126310579129731</v>
+        <v>-0.1283805066822665</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.370116263055813</v>
-      </c>
-      <c r="G4" s="2" t="n">
+        <v>-0.4219370509559131</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>46093</v>
+      <c r="H4" s="1" t="n">
+        <v>46111</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -588,22 +576,22 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3.329454071556786</v>
+        <v>3.329931859240454</v>
       </c>
       <c r="D5" t="n">
-        <v>3.140844883434637</v>
+        <v>2.714706428989373</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.05664868295779169</v>
+        <v>-0.1847561620649535</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.188609188122149</v>
-      </c>
-      <c r="G5" s="2" t="n">
+        <v>-0.6152254302510811</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>46093</v>
+      <c r="H5" s="1" t="n">
+        <v>46111</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -632,10 +620,10 @@
       <c r="F6" t="n">
         <v>0.1727296519235799</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="I6" t="inlineStr">
@@ -654,21 +642,21 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.387994716095842</v>
+        <v>3.38848090455584</v>
       </c>
       <c r="D7" t="n">
-        <v>3.497945305584181</v>
+        <v>3.498447272317835</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03245299910474486</v>
+        <v>0.03245299910474464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.109950589488339</v>
-      </c>
-      <c r="G7" s="2" t="n">
+        <v>0.1099663677619951</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="I7" t="inlineStr">
@@ -687,22 +675,22 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.235004527370492</v>
+        <v>3.235515355571837</v>
       </c>
       <c r="D8" t="n">
-        <v>2.95840753494462</v>
+        <v>2.541604067384476</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08550126903553312</v>
+        <v>-0.214467005076142</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2765969924258722</v>
-      </c>
-      <c r="G8" s="2" t="n">
+        <v>-0.6939112881873606</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>46093</v>
+      <c r="H8" s="1" t="n">
+        <v>46111</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -720,22 +708,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.17548743643422</v>
+        <v>3.175943129395937</v>
       </c>
       <c r="D9" t="n">
-        <v>3.230368234989983</v>
+        <v>3.065532450276418</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01728263759638393</v>
+        <v>-0.03476469024195616</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05488079855576311</v>
-      </c>
-      <c r="G9" s="2" t="n">
+        <v>-0.1104106791195187</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>46093</v>
+      <c r="H9" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -753,22 +741,22 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.249130017225665</v>
+        <v>3.249643075933495</v>
       </c>
       <c r="D10" t="n">
-        <v>3.057567410984722</v>
+        <v>3.338522793968391</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05895812270526268</v>
+        <v>0.02735060926940847</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.191562606240943</v>
-      </c>
-      <c r="G10" s="2" t="n">
+        <v>0.08887971803489592</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>46093</v>
+      <c r="H10" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -779,29 +767,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>3.759071275231678</v>
+        <v>2.960599032801569</v>
       </c>
       <c r="D11" t="n">
-        <v>3.409826647547095</v>
+        <v>3.767856803671825</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.09290715767634883</v>
+        <v>0.2726670386385828</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3492446276845831</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>46093</v>
+        <v>0.807257770870256</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -812,29 +800,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3.804333266358582</v>
+        <v>3.760263969100324</v>
       </c>
       <c r="D12" t="n">
-        <v>3.442920768870137</v>
+        <v>3.009625174957436</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.09500022006073638</v>
+        <v>-0.1996239626556019</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3614124974884452</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>46052</v>
+        <v>-0.7506387941428883</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>46111</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -845,29 +833,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3.788278868646771</v>
+        <v>2.764070383927569</v>
       </c>
       <c r="D13" t="n">
-        <v>3.786683915786489</v>
+        <v>2.881546450534193</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0004210230860992592</v>
+        <v>0.04250111259457068</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.001594952860282106</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>46052</v>
+        <v>0.1174760666066237</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -878,29 +866,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>3.431923038373986</v>
+        <v>3.804333266358582</v>
       </c>
       <c r="D14" t="n">
-        <v>3.26700776083725</v>
+        <v>3.442920768870137</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04805331462644669</v>
+        <v>-0.09500022006073638</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.164915277536736</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46054</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>46093</v>
+        <v>-0.3614124974884452</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>46052</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -911,61 +899,61 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOLDBEES</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>2.837635357851071</v>
       </c>
       <c r="D15" t="n">
-        <v>13.15136697408715</v>
+        <v>3.246925671773397</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1232422017275233</v>
+        <v>0.144236401900588</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.84863302591285</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>46093</v>
+        <v>0.4092903139223258</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>EQUITIES</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>3.78292066344223</v>
+        <v>3.788278868646771</v>
       </c>
       <c r="D16" t="n">
-        <v>3.526090715924211</v>
+        <v>3.786683915786489</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06789197299324778</v>
+        <v>-0.0004210230860992592</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2568299475180189</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="H16" s="2" t="n">
+        <v>-0.001594952860282106</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H16" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="I16" t="inlineStr">
@@ -977,29 +965,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>3.685009032403749</v>
+        <v>3.432415530693685</v>
       </c>
       <c r="D17" t="n">
-        <v>2.899189906288812</v>
+        <v>3.551604986161474</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2132475440914574</v>
+        <v>0.03472465801473068</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7858191261149372</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>46080</v>
+        <v>0.1191894554677888</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1010,29 +998,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>3.823487731800146</v>
+        <v>2.859439210863806</v>
       </c>
       <c r="D18" t="n">
-        <v>3.361000890760385</v>
+        <v>2.98144665065342</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1209594154554842</v>
+        <v>0.04266831038969943</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4624868410397607</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>46052</v>
+        <v>0.122007439789614</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1043,62 +1031,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>GOLDBEES</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>3.761133102424543</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>4.363016452251357</v>
+        <v>12.23543078698359</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1600271336951147</v>
+        <v>-0.184304614201094</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6018833498268141</v>
-      </c>
-      <c r="G19" s="2" t="n">
+        <v>-2.76456921301641</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H19" s="2" t="n">
-        <v>46093</v>
+      <c r="H19" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EQUITIES</t>
+          <t>GOLD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>GPIL</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>3.026236708377632</v>
+        <v>3.784120924344594</v>
       </c>
       <c r="D20" t="n">
-        <v>2.661118787617176</v>
+        <v>3.527209488745807</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1206508135168963</v>
+        <v>-0.06789197299324778</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.365117920760456</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>46054</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>46093</v>
+        <v>-0.2569114355987869</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>46052</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1109,28 +1097,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>HBLENGINE</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>3.141965515216141</v>
+        <v>3.685009032403749</v>
       </c>
       <c r="D21" t="n">
-        <v>3.327694751951424</v>
+        <v>2.899189906288812</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05911243641466446</v>
+        <v>-0.2132475440914574</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1857292367352827</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>46054</v>
-      </c>
-      <c r="H21" s="2" t="n">
+        <v>-0.7858191261149372</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H21" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="I21" t="inlineStr">
@@ -1142,28 +1130,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>3.836932140511178</v>
+        <v>3.823487731800146</v>
       </c>
       <c r="D22" t="n">
-        <v>3.269539886676219</v>
+        <v>3.361000890760385</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.147876541220082</v>
+        <v>-0.1209594154554842</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5673922538349587</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="H22" s="2" t="n">
+        <v>-0.4624868410397607</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H22" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="I22" t="inlineStr">
@@ -1175,29 +1163,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>3.823685722493536</v>
+        <v>3.761133102424543</v>
       </c>
       <c r="D23" t="n">
-        <v>3.60779948290721</v>
+        <v>4.921295150915387</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.05646024680227646</v>
+        <v>0.3084607794770589</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2158862395863257</v>
-      </c>
-      <c r="G23" s="2" t="n">
+        <v>1.160162048490843</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H23" s="2" t="n">
-        <v>46022</v>
+      <c r="H23" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1208,29 +1196,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>3.203380626262871</v>
+        <v>3.026670983365678</v>
       </c>
       <c r="D24" t="n">
-        <v>3.472561101113994</v>
+        <v>2.290521970723963</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08403012512601538</v>
+        <v>-0.2432206925323321</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2691804748511228</v>
-      </c>
-      <c r="G24" s="2" t="n">
+        <v>-0.736149012641715</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H24" s="2" t="n">
-        <v>46093</v>
+      <c r="H24" s="1" t="n">
+        <v>46111</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1241,29 +1229,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>3.156931568033881</v>
+        <v>3.142416397671167</v>
       </c>
       <c r="D25" t="n">
-        <v>2.820281504109771</v>
+        <v>3.328172287166903</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.106638378649992</v>
+        <v>0.05911243641466446</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3366500639241101</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>46083</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>46093</v>
+        <v>0.1857558894957361</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>46080</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1274,29 +1262,29 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>3.880168148124581</v>
+        <v>3.838149538401064</v>
       </c>
       <c r="D26" t="n">
-        <v>3.763383836301609</v>
+        <v>3.270577259976859</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.03009774508855179</v>
+        <v>-0.1478765412200824</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1167843118229719</v>
-      </c>
-      <c r="G26" s="2" t="n">
+        <v>-0.5675722784242052</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>46080</v>
+      <c r="H26" s="1" t="n">
+        <v>46052</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1307,29 +1295,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>3.84062906773262</v>
+        <v>3.823685722493536</v>
       </c>
       <c r="D27" t="n">
-        <v>3.700274599898645</v>
+        <v>3.60779948290721</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.03654465592972134</v>
+        <v>-0.05646024680227646</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.140354467833975</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>46052</v>
+        <v>-0.2158862395863257</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>46022</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1340,29 +1328,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>3.742909778445727</v>
+        <v>3.203840321989688</v>
       </c>
       <c r="D28" t="n">
-        <v>3.508750666602026</v>
+        <v>3.422331478384643</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.06256071497960003</v>
+        <v>0.06819664353910904</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.234159111843701</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>46052</v>
+        <v>0.218491156394955</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1373,29 +1361,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>18.99949059054711</v>
+        <v>3.157430068008463</v>
       </c>
       <c r="D29" t="n">
-        <v>19.02135421608283</v>
+        <v>2.386890911776818</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001150747986190526</v>
+        <v>-0.2440399754340908</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02186362553571897</v>
-      </c>
-      <c r="G29" s="2" t="n">
+        <v>-0.7705391562316453</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>46083</v>
       </c>
-      <c r="H29" s="2" t="n">
-        <v>46093</v>
+      <c r="H29" s="1" t="n">
+        <v>46111</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1406,29 +1394,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3.711581559148391</v>
+        <v>3.881399264115936</v>
       </c>
       <c r="D30" t="n">
-        <v>3.437850168080679</v>
+        <v>3.764577898477682</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.07375060650169807</v>
+        <v>-0.03009774508855179</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2737313910677122</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>46052</v>
+        <v>-0.1168213656382537</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>46080</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1439,29 +1427,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>3.784445993602887</v>
+        <v>3.841847638599049</v>
       </c>
       <c r="D31" t="n">
-        <v>3.729701468055442</v>
+        <v>3.701448638512034</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.01446566436407959</v>
+        <v>-0.03654465592972145</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.05474452554744502</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>46022</v>
+        <v>-0.1403990000870152</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>46052</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1472,29 +1460,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>3.710165389269866</v>
+        <v>2.793983208286505</v>
       </c>
       <c r="D32" t="n">
-        <v>3.486789027833802</v>
+        <v>2.8078645708084</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.06020657787442274</v>
+        <v>0.004968305636456671</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2233763614360642</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>46093</v>
+        <v>0.0138813625218952</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1505,29 +1493,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>3.181410155140579</v>
+        <v>3.742909778445727</v>
       </c>
       <c r="D33" t="n">
-        <v>2.946715963367914</v>
+        <v>3.508750666602026</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.07377049180327844</v>
+        <v>-0.06256071497960003</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.234694191772665</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>46083</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>46093</v>
+        <v>-0.234159111843701</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>46052</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1538,29 +1526,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>3.796462264150943</v>
+        <v>18.99949059054711</v>
       </c>
       <c r="D34" t="n">
-        <v>3.937971698113207</v>
+        <v>19.14076324785487</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03727402621606513</v>
+        <v>0.007435602372310335</v>
       </c>
       <c r="F34" t="n">
-        <v>0.141509433962264</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>46022</v>
+        <v>0.1412726573077592</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1571,29 +1559,29 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>3.800814016975232</v>
+        <v>3.711581559148391</v>
       </c>
       <c r="D35" t="n">
-        <v>4.145530351913434</v>
+        <v>3.437850168080679</v>
       </c>
       <c r="E35" t="n">
-        <v>0.09069539666993109</v>
+        <v>-0.07375060650169807</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3447163349382025</v>
-      </c>
-      <c r="G35" s="2" t="n">
+        <v>-0.2737313910677122</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H35" s="2" t="n">
-        <v>46022</v>
+      <c r="H35" s="1" t="n">
+        <v>46052</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1604,29 +1592,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>3.060029768855503</v>
+        <v>3.784445993602887</v>
       </c>
       <c r="D36" t="n">
-        <v>3.409426442413982</v>
+        <v>3.729701468055442</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1141808086687859</v>
+        <v>-0.01446566436407959</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3493966735584793</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>46054</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>46093</v>
+        <v>-0.05474452554744502</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>46022</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1637,62 +1625,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MOGSEC</t>
+          <t>M&amp;MFIN</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3.710165389269866</v>
       </c>
       <c r="D37" t="n">
-        <v>18.99949059054711</v>
+        <v>2.885235982250907</v>
       </c>
       <c r="E37" t="n">
-        <v>2.799898118109422</v>
+        <v>-0.2223430279967382</v>
       </c>
       <c r="F37" t="n">
-        <v>13.99949059054711</v>
-      </c>
-      <c r="G37" s="2" t="n">
+        <v>-0.824929407018959</v>
+      </c>
+      <c r="G37" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H37" s="2" t="n">
-        <v>46080</v>
+      <c r="H37" s="1" t="n">
+        <v>46111</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DEBT</t>
+          <t>EQUITIES</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>3.8170036322846</v>
+        <v>3.181912520442865</v>
       </c>
       <c r="D38" t="n">
-        <v>3.817604561722133</v>
+        <v>3.449797903519883</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001574348613269105</v>
+        <v>0.0841900527924424</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0006009294375330931</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>46022</v>
+        <v>0.2678853830770183</v>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1703,29 +1691,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>3.159462895412427</v>
+        <v>3.800814016975232</v>
       </c>
       <c r="D39" t="n">
-        <v>3.03319653596106</v>
+        <v>4.145530351913434</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.03996450144570673</v>
+        <v>0.09069539666993109</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.1262663594513667</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>46054</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>46080</v>
+        <v>0.3447163349382025</v>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>46022</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1736,29 +1724,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>3.805100392337872</v>
+        <v>3.060468893259622</v>
       </c>
       <c r="D40" t="n">
-        <v>5.684571890145388</v>
+        <v>3.983145517910004</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4939347990902179</v>
+        <v>0.3014821116733077</v>
       </c>
       <c r="F40" t="n">
-        <v>1.879471497807516</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>46093</v>
+        <v>0.9226766246503821</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1769,61 +1757,61 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>MOGSEC</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>3.716190939358797</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>3.331805768583291</v>
+        <v>18.99949059054711</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.1034352585881471</v>
+        <v>2.799898118109422</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.3843851707755062</v>
-      </c>
-      <c r="G41" s="2" t="n">
+        <v>13.99949059054711</v>
+      </c>
+      <c r="G41" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H41" s="2" t="n">
-        <v>46052</v>
+      <c r="H41" s="1" t="n">
+        <v>46080</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>EQUITIES</t>
+          <t>DEBT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>3.884029986369832</v>
+        <v>3.8170036322846</v>
       </c>
       <c r="D42" t="n">
-        <v>3.68838028169014</v>
+        <v>3.817604561722133</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.05037286152946363</v>
+        <v>0.0001574348613269105</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1956497046796919</v>
-      </c>
-      <c r="G42" s="2" t="n">
+        <v>0.0006009294375330931</v>
+      </c>
+      <c r="G42" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="I42" t="inlineStr">
@@ -1835,29 +1823,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>3.715361445783132</v>
+        <v>3.159916288799448</v>
       </c>
       <c r="D43" t="n">
-        <v>3.824799196787149</v>
+        <v>3.033631809707409</v>
       </c>
       <c r="E43" t="n">
-        <v>0.02945547898932599</v>
+        <v>-0.03996450144570707</v>
       </c>
       <c r="F43" t="n">
-        <v>0.109437751004017</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>46022</v>
+        <v>-0.126284479092039</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>46080</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -1868,29 +1856,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>3.724464832514145</v>
+        <v>3.805100392337872</v>
       </c>
       <c r="D44" t="n">
-        <v>3.237087492803483</v>
+        <v>6.246393953381022</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.1308583545898767</v>
+        <v>0.6415845337376784</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.4873773397106618</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>46052</v>
+        <v>2.441293561043151</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -1901,29 +1889,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>3.40652398078372</v>
+        <v>2.712757634490163</v>
       </c>
       <c r="D45" t="n">
-        <v>3.46657304779343</v>
+        <v>3.018695912625819</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01762766601628174</v>
+        <v>0.112777593636062</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06004906700971002</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>46054</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>46093</v>
+        <v>0.3059382781356561</v>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -1934,29 +1922,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>3.785201970097795</v>
+        <v>3.716190939358797</v>
       </c>
       <c r="D46" t="n">
-        <v>4.141716296298934</v>
+        <v>3.331805768583291</v>
       </c>
       <c r="E46" t="n">
-        <v>0.09418634171109441</v>
+        <v>-0.1034352585881471</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3565143262011388</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>46093</v>
+        <v>-0.3843851707755062</v>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>46052</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -1967,29 +1955,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>3.864460563156646</v>
+        <v>2.803621051141296</v>
       </c>
       <c r="D47" t="n">
-        <v>3.883409570527229</v>
+        <v>2.94134449454921</v>
       </c>
       <c r="E47" t="n">
-        <v>0.004903402961655479</v>
+        <v>0.04912341607359871</v>
       </c>
       <c r="F47" t="n">
-        <v>0.01894900737058292</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>46093</v>
+        <v>0.1377234434079142</v>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2000,61 +1988,61 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SILVERBEES</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>3.884029986369832</v>
       </c>
       <c r="D48" t="n">
-        <v>8.618013356597075</v>
+        <v>3.68838028169014</v>
       </c>
       <c r="E48" t="n">
-        <v>0.723602671319415</v>
+        <v>-0.05037286152946363</v>
       </c>
       <c r="F48" t="n">
-        <v>3.618013356597075</v>
-      </c>
-      <c r="G48" s="2" t="n">
+        <v>-0.1956497046796919</v>
+      </c>
+      <c r="G48" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H48" s="2" t="n">
-        <v>46052</v>
+      <c r="H48" s="1" t="n">
+        <v>46022</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>EQUITIES</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>3.71708320633953</v>
+        <v>3.715361445783132</v>
       </c>
       <c r="D49" t="n">
-        <v>3.351798232246265</v>
+        <v>3.824799196787149</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.09827193899514197</v>
+        <v>0.02945547898932599</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.3652849740932651</v>
-      </c>
-      <c r="G49" s="2" t="n">
+        <v>0.109437751004017</v>
+      </c>
+      <c r="G49" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H49" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="I49" t="inlineStr">
@@ -2066,29 +2054,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>3.245561253581092</v>
+        <v>3.725646546305792</v>
       </c>
       <c r="D50" t="n">
-        <v>3.428755240616786</v>
+        <v>3.238114569472759</v>
       </c>
       <c r="E50" t="n">
-        <v>0.05644447068548186</v>
+        <v>-0.1308583545898767</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1831939870356938</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>46054</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>46093</v>
+        <v>-0.4875319768330328</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>46052</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2099,31 +2087,295 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.407012828254553</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3.470967385146365</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.01877144587230006</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.06395455689181206</v>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3.786402954822684</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4.201282750532631</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.1095709570957102</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.4148797957099468</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.865686695379694</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3.652632275177342</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.05511424928900643</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.2130544202023521</v>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SILVERBEES</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8.618013356597075</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.723602671319415</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.618013356597075</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3.71708320633953</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3.351798232246265</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.09827193899514197</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.3652849740932651</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2.83693800509724</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3.665253461824459</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.2919751701443427</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.8283154567272191</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3.888361885884186</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3.949950445986128</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.01583920476268563</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.06158856010194169</v>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.246027002367597</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.268067098327462</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.006789868335595806</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.022040095959865</v>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>EQUITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>VEDL</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>3.764468808263581</v>
-      </c>
-      <c r="D51" t="n">
-        <v>4.415981455242576</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.173068945490749</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.6515126469789947</v>
-      </c>
-      <c r="G51" s="2" t="n">
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3.7656632146841</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4.611086317557672</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2245084211399651</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.8454231028735721</v>
+      </c>
+      <c r="G59" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="H51" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="I51" t="inlineStr">
+      <c r="H59" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>EQUITIES</t>
         </is>
